--- a/entertainment_forms/024_fictional_pets_quiz_template--entertainment_forms.xlsx
+++ b/entertainment_forms/024_fictional_pets_quiz_template--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'submit',_'value':_1}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Submit', 'value': 1}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'save_and_continue',_'value':_2}</t>
+          <t>save_and_continue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Save and Continue', 'value': 2}</t>
+          <t>Save and Continue</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'cancel',_'value':_3}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel', 'value': 3}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_1}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 1}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_2}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 2}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'maybe',_'value':_3}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe', 'value': 3}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_1}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 1}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'maybe',_'value':_2}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe', 'value': 2}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_3}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 3}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
